--- a/backend/api/api/domain/data/Performance.xlsx
+++ b/backend/api/api/domain/data/Performance.xlsx
@@ -5,17 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cityd\Documents\GitHub\the-private-ledger\backend\api\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cityd\Documents\GitHub\the-private-ledger\backend\api\api\domain\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5E1D47-A8BE-470A-84EB-05C98ACDD67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B71BBFB-D611-4E8E-B30C-9283F74471F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{8CCB27D2-2797-46F7-8043-BF3A4CB24308}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{8CCB27D2-2797-46F7-8043-BF3A4CB24308}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -882,15 +880,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{599582BA-7042-4229-9E6A-4967419D623E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D83909-4C0C-4F0F-9121-B70065C38E0B}">
   <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1648,7 +1637,9 @@
       <c r="E29" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4">
+        <v>0</v>
+      </c>
       <c r="G29" s="6">
         <v>11.1</v>
       </c>
@@ -2270,7 +2261,9 @@
       <c r="E53" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="4"/>
+      <c r="F53" s="4">
+        <v>0</v>
+      </c>
       <c r="G53" s="6">
         <v>11.98</v>
       </c>
@@ -2334,13 +2327,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C8196A-B479-4F21-8C92-F553FF75CE31}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>